--- a/docs/2026ESWContest_자유공모_파인더_참가신청서.xlsx
+++ b/docs/2026ESWContest_자유공모_파인더_참가신청서.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자동차모빌리티 참가신청서" sheetId="2" r:id="R909adabeea3d4dbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자동차모빌리티 참가신청서" sheetId="2" r:id="R2f85cd41e630441a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1309,7 +1309,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="C6" s="19" t="str">
-        <x:v>김민수</x:v>
+        <x:v>이휘</x:v>
       </x:c>
       <x:c r="D6" s="20"/>
       <x:c r="E6" s="20"/>
@@ -1325,19 +1325,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="C7" s="2" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="2" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="H7" s="26"/>
     </x:row>
@@ -1347,19 +1347,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="3" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="10" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="28" t="str">
-        <x:v>[확인 필요]</x:v>
+        <x:v>[직접 입력]</x:v>
       </x:c>
       <x:c r="H8" s="26"/>
     </x:row>
@@ -1380,7 +1380,9 @@
       <x:c r="B10" s="1" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C10" s="19"/>
+      <x:c r="C10" s="19" t="str">
+        <x:v>김민수</x:v>
+      </x:c>
       <x:c r="D10" s="20"/>
       <x:c r="E10" s="20"/>
       <x:c r="F10" s="20"/>
@@ -1394,15 +1396,21 @@
       <x:c r="B11" s="1" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C11" s="2"/>
+      <x:c r="C11" s="2" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="D11" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E11" s="2"/>
+      <x:c r="E11" s="2" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="F11" s="1" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G11" s="6"/>
+      <x:c r="G11" s="6" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="H11" s="27"/>
     </x:row>
     <x:row r="12" ht="16.5" customHeight="1">
@@ -1410,15 +1418,21 @@
       <x:c r="B12" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C12" s="3"/>
+      <x:c r="C12" s="3" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="D12" s="1" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E12" s="10"/>
+      <x:c r="E12" s="10" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="F12" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G12" s="28"/>
+      <x:c r="G12" s="28" t="str">
+        <x:v>[직접 입력]</x:v>
+      </x:c>
       <x:c r="H12" s="27"/>
     </x:row>
     <x:row r="13" ht="3.75" customHeight="1">
@@ -1640,7 +1654,7 @@
       <x:c r="D28" s="11"/>
       <x:c r="E28" s="11"/>
       <x:c r="F28" s="22" t="str">
-        <x:v>팀장 김민수</x:v>
+        <x:v>팀장 이휘</x:v>
       </x:c>
       <x:c r="G28" s="22"/>
       <x:c r="H28" s="5"/>
@@ -1679,6 +1693,6 @@
     <x:mergeCell ref="C22:G22"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd969dcf16214ab7"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3432d94cc26e4677"/>
 </x:worksheet>
 </file>